--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -7890,7 +7890,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46209.56550644676</v>
+        <v>46279.16317537037</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>283</v>
@@ -7934,8 +7934,8 @@
       <c r="R104" s="5">
         <v>46286</v>
       </c>
-      <c r="S104" s="7" t="s">
-        <v>33</v>
+      <c r="S104" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -388,559 +388,559 @@
     <t>Generación OC Alabe ot 4332,Fabricación Alabe ot 4332</t>
   </si>
   <si>
+    <t>1214937218513477</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4332</t>
+  </si>
+  <si>
+    <t>Alabe ot 4332,Fabricación Alabe ot 4332</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214937218513495</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4332</t>
+  </si>
+  <si>
+    <t>Alabe ot 4332,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214937301045314</t>
+  </si>
+  <si>
+    <t>rodete ot 4332</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4332,Fabricación Rodete ot 4332</t>
+  </si>
+  <si>
+    <t>1214937301045329</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4332</t>
+  </si>
+  <si>
+    <t>rodete ot 4332,Fabricación Rodete ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151080525</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4332</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151080543</t>
+  </si>
+  <si>
+    <t>Motor ot 4332</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4332,Planos motor proveedor ot 4332,Generación OC motor ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151080846</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4332</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4332,Planos motor proveedor ot 4332,Motor ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151080864</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4332</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Motor ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509207065</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4332</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Motor ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509211289</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser ot 4332</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4332,Fabricacion Corte Laser  ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509211304</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4332</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser ot 4332,Fabricacion Corte Laser  ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509215584</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  ot 4332</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509215602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma ot 4332 </t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  ot 4332,Generación OC Corte Plasma  ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151048327</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma ot 4332 ,Fabricación Corte Plasma  ot 4332</t>
+  </si>
+  <si>
+    <t>1214952151048342</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  ot 4332</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma ot 4332 ,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214937218638193</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4332</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa ot 4332,Fabricación estructura proveedor externo ot 4332</t>
+  </si>
+  <si>
+    <t>1214937218638203</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4332,Fabricación estructura proveedor externo ot 4332</t>
+  </si>
+  <si>
+    <t>1214937218653848</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4332</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  ot 4332,Control de calidad fabricación externa  ot 4332</t>
+  </si>
+  <si>
+    <t>1214937218653863</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4332</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214937218653873</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4332</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4332,Fabricación Mecanizado ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509338287</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4332,Fabricación Mecanizado ot 4332</t>
+  </si>
+  <si>
+    <t>1214937509338302</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4332</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4332,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214922681023458</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214937509347700</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214937509347720</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4332,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214937218721335</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Propuesta Fabricación externa  ot 4332,propuesta Corte Laser ot 4332,Propuesta Corte plasma  ot 4332,Propuesta Mecanizado ot 4332,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214937301242618</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214937201391812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214922681023542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214922681023543</t>
+  </si>
+  <si>
+    <t>1214922681023544</t>
+  </si>
+  <si>
+    <t>1214922681023545</t>
+  </si>
+  <si>
+    <t>1214922681023546</t>
+  </si>
+  <si>
+    <t>1214922681023547</t>
+  </si>
+  <si>
+    <t>1214922681023548</t>
+  </si>
+  <si>
+    <t>1214922681023549</t>
+  </si>
+  <si>
+    <t>1214922681023550</t>
+  </si>
+  <si>
+    <t>1214937201391822</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214937201391832</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214937201399321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214937201399341</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214937509388810</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214937509388825</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214937509391978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214937509391993</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214937509401231</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
+  </si>
+  <si>
+    <t>1214937509401251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214922681023460</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214922681023461</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma,Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214922681023462</t>
+  </si>
+  <si>
+    <t>1214922681023463</t>
+  </si>
+  <si>
+    <t>1214922681023464</t>
+  </si>
+  <si>
+    <t>1214922681023465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214922681023466</t>
+  </si>
+  <si>
+    <t>1214922681023467</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma,Control de calidad corte laser ,Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214922681023468</t>
+  </si>
+  <si>
+    <t>1214937218773374</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214937301299083</t>
+  </si>
+  <si>
+    <t>OT 4332 -  ZVN 1-16-126/4 ,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214922681023469</t>
+  </si>
+  <si>
+    <t>1214922681023470</t>
+  </si>
+  <si>
+    <t>1214922681023471</t>
+  </si>
+  <si>
+    <t>1214922681023472</t>
+  </si>
+  <si>
+    <t>1214922681023473</t>
+  </si>
+  <si>
+    <t>1214922681023474</t>
+  </si>
+  <si>
+    <t>1214922681023475</t>
+  </si>
+  <si>
+    <t>1214922681023476</t>
+  </si>
+  <si>
+    <t>1214922681023477</t>
+  </si>
+  <si>
+    <t>1214937301299103</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214937301301272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,Control de calidad Armado,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214922681023479</t>
+  </si>
+  <si>
+    <t>1214922681023480</t>
+  </si>
+  <si>
+    <t>1214922681023481</t>
+  </si>
+  <si>
+    <t>1214922681023482</t>
+  </si>
+  <si>
+    <t>1214922681023483</t>
+  </si>
+  <si>
+    <t>1214922681023484</t>
+  </si>
+  <si>
+    <t>1214922681023485</t>
+  </si>
+  <si>
+    <t>1214922681023478</t>
+  </si>
+  <si>
+    <t>1214922681023541</t>
+  </si>
+  <si>
+    <t>1214937201506803</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214937201506813</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:</t>
+  </si>
+  <si>
+    <t>1214937301349940</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:,OT 4332 -  ZVN 1-16-126/4 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214937218513477</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4332</t>
-  </si>
-  <si>
-    <t>Alabe ot 4332,Fabricación Alabe ot 4332</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214937218513495</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4332</t>
-  </si>
-  <si>
-    <t>Alabe ot 4332,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214937301045314</t>
-  </si>
-  <si>
-    <t>rodete ot 4332</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4332,Fabricación Rodete ot 4332</t>
-  </si>
-  <si>
-    <t>1214937301045329</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4332</t>
-  </si>
-  <si>
-    <t>rodete ot 4332,Fabricación Rodete ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151080525</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4332</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151080543</t>
-  </si>
-  <si>
-    <t>Motor ot 4332</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4332,Planos motor proveedor ot 4332,Generación OC motor ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151080846</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4332</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4332,Planos motor proveedor ot 4332,Motor ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151080864</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4332</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509207065</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4332</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Motor ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509211289</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4332,Fabricacion Corte Laser  ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509211304</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser ot 4332,Fabricacion Corte Laser  ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509215584</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  ot 4332</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509215602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma ot 4332 </t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  ot 4332,Generación OC Corte Plasma  ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151048327</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma ot 4332 ,Fabricación Corte Plasma  ot 4332</t>
-  </si>
-  <si>
-    <t>1214952151048342</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  ot 4332</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma ot 4332 ,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214937218638193</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4332</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa ot 4332,Fabricación estructura proveedor externo ot 4332</t>
-  </si>
-  <si>
-    <t>1214937218638203</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4332,Fabricación estructura proveedor externo ot 4332</t>
-  </si>
-  <si>
-    <t>1214937218653848</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4332</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  ot 4332,Control de calidad fabricación externa  ot 4332</t>
-  </si>
-  <si>
-    <t>1214937218653863</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4332</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214937218653873</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4332</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4332,Fabricación Mecanizado ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509338287</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4332,Fabricación Mecanizado ot 4332</t>
-  </si>
-  <si>
-    <t>1214937509338302</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4332</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4332,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214922681023458</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214937509347700</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214937509347720</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4332,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214937218721335</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Propuesta Fabricación externa  ot 4332,propuesta Corte Laser ot 4332,Propuesta Corte plasma  ot 4332,Propuesta Mecanizado ot 4332,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214937301242618</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214937201391812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214922681023542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214922681023543</t>
-  </si>
-  <si>
-    <t>1214922681023544</t>
-  </si>
-  <si>
-    <t>1214922681023545</t>
-  </si>
-  <si>
-    <t>1214922681023546</t>
-  </si>
-  <si>
-    <t>1214922681023547</t>
-  </si>
-  <si>
-    <t>1214922681023548</t>
-  </si>
-  <si>
-    <t>1214922681023549</t>
-  </si>
-  <si>
-    <t>1214922681023550</t>
-  </si>
-  <si>
-    <t>1214937201391822</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214937201391832</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214937201399321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214937201399341</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214937509388810</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214937509388825</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214937509391978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214937509391993</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214937509401231</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
-  </si>
-  <si>
-    <t>1214937509401251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214922681023460</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214922681023461</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma,Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214922681023462</t>
-  </si>
-  <si>
-    <t>1214922681023463</t>
-  </si>
-  <si>
-    <t>1214922681023464</t>
-  </si>
-  <si>
-    <t>1214922681023465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214922681023466</t>
-  </si>
-  <si>
-    <t>1214922681023467</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma,Control de calidad corte laser ,Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214922681023468</t>
-  </si>
-  <si>
-    <t>1214937218773374</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214937301299083</t>
-  </si>
-  <si>
-    <t>OT 4332 -  ZVN 1-16-126/4 ,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,OT 4332 -  ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214922681023469</t>
-  </si>
-  <si>
-    <t>1214922681023470</t>
-  </si>
-  <si>
-    <t>1214922681023471</t>
-  </si>
-  <si>
-    <t>1214922681023472</t>
-  </si>
-  <si>
-    <t>1214922681023473</t>
-  </si>
-  <si>
-    <t>1214922681023474</t>
-  </si>
-  <si>
-    <t>1214922681023475</t>
-  </si>
-  <si>
-    <t>1214922681023476</t>
-  </si>
-  <si>
-    <t>1214922681023477</t>
-  </si>
-  <si>
-    <t>1214937301299103</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214937301301272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Control de calidad Armado,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214922681023479</t>
-  </si>
-  <si>
-    <t>1214922681023480</t>
-  </si>
-  <si>
-    <t>1214922681023481</t>
-  </si>
-  <si>
-    <t>1214922681023482</t>
-  </si>
-  <si>
-    <t>1214922681023483</t>
-  </si>
-  <si>
-    <t>1214922681023484</t>
-  </si>
-  <si>
-    <t>1214922681023485</t>
-  </si>
-  <si>
-    <t>1214922681023478</t>
-  </si>
-  <si>
-    <t>1214922681023541</t>
-  </si>
-  <si>
-    <t>1214937201506803</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214937201506813</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:</t>
-  </si>
-  <si>
-    <t>1214937301349940</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Bodega:,OT 4332 -  ZVN 1-16-126/4 </t>
   </si>
   <si>
     <t>1214937301349960</t>
@@ -3241,7 +3241,7 @@
         <v>46209.565500937504</v>
       </c>
       <c r="D23" s="9">
-        <v>46274.139835532405</v>
+        <v>46282.12938302083</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -3285,8 +3285,8 @@
       <c r="R23" s="9">
         <v>46281</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>100</v>
+      <c r="S23" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3309,7 +3309,7 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3342,7 +3342,7 @@
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3353,12 +3353,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3370,7 +3370,7 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3400,10 +3400,10 @@
         <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3414,12 +3414,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3431,7 +3431,7 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3461,7 +3461,7 @@
         <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>93</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3496,7 +3496,7 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3523,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3540,12 +3540,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3557,7 +3557,7 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3584,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3601,12 +3601,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3616,7 +3616,7 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3646,7 +3646,7 @@
         <v>93</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>93</v>
@@ -3664,12 +3664,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3681,7 +3681,7 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3708,13 +3708,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3725,12 +3725,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3740,7 +3740,7 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3767,13 +3767,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3784,12 +3784,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3801,7 +3801,7 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3828,13 +3828,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3845,12 +3845,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3862,16 +3862,16 @@
         <v>46239.17676671296</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3892,7 +3892,7 @@
         <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>93</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3927,16 +3927,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3954,13 +3954,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3971,12 +3971,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3988,16 +3988,16 @@
         <v>46243.806791828705</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -4015,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4032,12 +4032,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4049,16 +4049,16 @@
         <v>46239.176766689816</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4079,7 +4079,7 @@
         <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4120,10 +4120,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4141,13 +4141,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4169,16 +4169,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4196,13 +4196,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4224,16 +4224,16 @@
         <v>46235.19736361111</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4254,7 +4254,7 @@
         <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4295,10 +4295,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4316,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4344,16 +4344,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4371,13 +4371,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4397,16 +4397,16 @@
         <v>46265.16862525463</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4424,10 +4424,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4452,16 +4452,16 @@
         <v>46239.17676725694</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4482,7 +4482,7 @@
         <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4505,7 +4505,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4523,10 +4523,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4544,13 +4544,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4572,16 +4572,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4599,13 +4599,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4627,7 +4627,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4651,7 +4651,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4680,16 +4680,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4707,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4745,16 +4745,16 @@
         <v>46221.17370061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4772,13 +4772,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4816,10 +4816,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4837,13 +4837,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4873,16 +4873,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4900,10 +4900,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4921,12 +4921,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4936,16 +4936,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4961,13 +4961,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4987,16 +4987,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5012,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5038,16 +5038,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5063,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5079,7 +5079,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5089,16 +5089,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5114,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5140,16 +5140,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5165,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5191,16 +5191,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5216,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5242,16 +5242,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5267,13 +5267,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5283,7 +5283,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5293,16 +5293,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5318,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5334,7 +5334,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5344,16 +5344,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5369,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5395,16 +5395,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5420,13 +5420,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5448,7 +5448,7 @@
         <v>46245.81247094907</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5472,7 +5472,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5501,16 +5501,16 @@
         <v>46245.8106065162</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5528,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5566,16 +5566,16 @@
         <v>46245.81244717592</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5593,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5631,16 +5631,16 @@
         <v>46245.810639641204</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5658,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5696,16 +5696,16 @@
         <v>46245.81064041667</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5723,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5761,16 +5761,16 @@
         <v>46245.81066096065</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5788,13 +5788,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5826,16 +5826,16 @@
         <v>46245.812459872686</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5853,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5889,7 +5889,7 @@
         <v>46269.60526216435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5913,7 +5913,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5928,7 +5928,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
@@ -5940,16 +5940,16 @@
         <v>46269.60495612268</v>
       </c>
       <c r="E69" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="10" t="s">
+      <c r="H69" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5967,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -6005,16 +6005,16 @@
         <v>46260.594822025465</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -6032,13 +6032,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6060,16 +6060,16 @@
         <v>46260.594834965275</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6087,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6115,16 +6115,16 @@
         <v>46260.59484337963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6170,16 +6170,16 @@
         <v>46260.59485025463</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6197,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6225,16 +6225,16 @@
         <v>46260.59485923611</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6252,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6280,16 +6280,16 @@
         <v>46260.594866377316</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6307,13 +6307,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6323,7 +6323,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6335,16 +6335,16 @@
         <v>46260.594872939815</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6362,13 +6362,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6390,16 +6390,16 @@
         <v>46260.594889444445</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6417,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6445,16 +6445,16 @@
         <v>46260.59489903935</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6472,13 +6472,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6500,16 +6500,16 @@
         <v>46260.59490708333</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6527,13 +6527,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6555,16 +6555,16 @@
         <v>46274.15756821759</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6582,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6620,16 +6620,16 @@
         <v>46260.595147361106</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6647,13 +6647,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>254</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6663,7 +6663,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6675,16 +6675,16 @@
         <v>46260.59515282407</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6702,13 +6702,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6718,7 +6718,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6730,16 +6730,16 @@
         <v>46260.59515949074</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6757,13 +6757,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6773,7 +6773,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6785,16 +6785,16 @@
         <v>46260.59516693287</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6812,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6840,16 +6840,16 @@
         <v>46260.59518276621</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6867,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6895,16 +6895,16 @@
         <v>46260.59518892361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6922,13 +6922,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6938,7 +6938,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6950,16 +6950,16 @@
         <v>46260.5952615625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6977,13 +6977,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -7005,16 +7005,16 @@
         <v>46260.59523880787</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -7032,13 +7032,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -7060,16 +7060,16 @@
         <v>46260.595230810184</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7087,13 +7087,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7103,7 +7103,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7115,16 +7115,16 @@
         <v>46260.595220324074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7142,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7170,16 +7170,16 @@
         <v>46276.13492725695</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7197,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7235,16 +7235,16 @@
         <v>46269.60505780093</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7262,13 +7262,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7278,7 +7278,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7290,16 +7290,16 @@
         <v>46269.605069467594</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7317,13 +7317,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7345,16 +7345,16 @@
         <v>46269.60507532407</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7372,13 +7372,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7400,16 +7400,16 @@
         <v>46269.60508171296</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7427,13 +7427,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7443,7 +7443,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7455,16 +7455,16 @@
         <v>46269.60508763889</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7482,13 +7482,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7498,7 +7498,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7510,16 +7510,16 @@
         <v>46269.605092997685</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7537,13 +7537,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7565,16 +7565,16 @@
         <v>46269.60509805556</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7592,13 +7592,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7620,16 +7620,16 @@
         <v>46269.60523311343</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7647,13 +7647,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7663,7 +7663,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7675,16 +7675,16 @@
         <v>46269.60521418981</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7702,13 +7702,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7718,7 +7718,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7730,16 +7730,16 @@
         <v>46269.60520842593</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7757,13 +7757,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7783,7 +7783,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7807,7 +7807,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7830,16 +7830,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7857,13 +7857,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7883,7 +7883,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7893,16 +7893,16 @@
         <v>46279.16317537037</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7920,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7935,7 +7935,7 @@
         <v>46286</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>100</v>
+        <v>284</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7962,10 +7962,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7983,10 +7983,10 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>287</v>
@@ -8004,7 +8004,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -8025,10 +8025,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -8046,10 +8046,10 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>290</v>
@@ -8229,7 +8229,7 @@
         <v>296</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8251,7 +8251,7 @@
         <v>46269.61196905092</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8281,10 +8281,10 @@
         <v>295</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8306,7 +8306,7 @@
         <v>46269.6119777662</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8336,10 +8336,10 @@
         <v>295</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8361,7 +8361,7 @@
         <v>46269.61198565972</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8391,10 +8391,10 @@
         <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8416,7 +8416,7 @@
         <v>46269.611996921296</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8446,10 +8446,10 @@
         <v>295</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8471,7 +8471,7 @@
         <v>46269.61200453703</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8501,10 +8501,10 @@
         <v>295</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8526,7 +8526,7 @@
         <v>46269.612009375</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8556,10 +8556,10 @@
         <v>295</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8581,7 +8581,7 @@
         <v>46269.61201532408</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8611,10 +8611,10 @@
         <v>295</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8636,7 +8636,7 @@
         <v>46269.61202097222</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8666,10 +8666,10 @@
         <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8691,7 +8691,7 @@
         <v>46269.61203211806</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8721,10 +8721,10 @@
         <v>295</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8776,7 +8776,7 @@
         <v>292</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>292</v>
@@ -8811,7 +8811,7 @@
         <v>46269.61300940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8864,7 +8864,7 @@
         <v>46269.61197182871</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8897,7 +8897,7 @@
         <v>314</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8917,7 +8917,7 @@
         <v>46269.61198152778</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8950,7 +8950,7 @@
         <v>316</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8970,7 +8970,7 @@
         <v>46269.61198898148</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9003,7 +9003,7 @@
         <v>314</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9023,7 +9023,7 @@
         <v>46269.6120009838</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9056,7 +9056,7 @@
         <v>314</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9076,7 +9076,7 @@
         <v>46269.61200821759</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9109,7 +9109,7 @@
         <v>320</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9129,7 +9129,7 @@
         <v>46269.612014178245</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9162,7 +9162,7 @@
         <v>316</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9182,7 +9182,7 @@
         <v>46269.612017962965</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9215,7 +9215,7 @@
         <v>314</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9235,7 +9235,7 @@
         <v>46269.612024120375</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9268,7 +9268,7 @@
         <v>314</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9288,7 +9288,7 @@
         <v>46269.61203491898</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9321,7 +9321,7 @@
         <v>325</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9371,7 +9371,7 @@
         <v>292</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>292</v>
@@ -9406,7 +9406,7 @@
         <v>46269.61324065972</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9459,7 +9459,7 @@
         <v>46223.58385686342</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9492,7 +9492,7 @@
         <v>329</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9512,7 +9512,7 @@
         <v>46223.58385618056</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9545,7 +9545,7 @@
         <v>333</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9565,7 +9565,7 @@
         <v>46223.583855543984</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9598,7 +9598,7 @@
         <v>329</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9618,7 +9618,7 @@
         <v>46223.5838549537</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9651,7 +9651,7 @@
         <v>336</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9671,7 +9671,7 @@
         <v>46223.58385431713</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9704,7 +9704,7 @@
         <v>329</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9724,7 +9724,7 @@
         <v>46223.583853715274</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9757,7 +9757,7 @@
         <v>329</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9777,7 +9777,7 @@
         <v>46223.58385304398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9810,7 +9810,7 @@
         <v>340</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9830,7 +9830,7 @@
         <v>46223.58385228009</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9863,7 +9863,7 @@
         <v>333</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9883,7 +9883,7 @@
         <v>46223.58385163195</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9916,7 +9916,7 @@
         <v>329</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10052,7 +10052,7 @@
         <v>46223.583970949076</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10085,7 +10085,7 @@
         <v>346</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10105,7 +10105,7 @@
         <v>46223.583970277774</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10138,7 +10138,7 @@
         <v>346</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10158,7 +10158,7 @@
         <v>46223.583969479165</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10191,7 +10191,7 @@
         <v>351</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10211,7 +10211,7 @@
         <v>46223.58396876157</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10244,7 +10244,7 @@
         <v>353</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10264,7 +10264,7 @@
         <v>46223.5839677662</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10297,7 +10297,7 @@
         <v>353</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10317,7 +10317,7 @@
         <v>46223.58396645833</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10350,7 +10350,7 @@
         <v>353</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10370,7 +10370,7 @@
         <v>46223.58396577546</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10403,7 +10403,7 @@
         <v>353</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10423,7 +10423,7 @@
         <v>46223.58396513889</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10456,7 +10456,7 @@
         <v>353</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10476,7 +10476,7 @@
         <v>46223.583964537036</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10509,7 +10509,7 @@
         <v>353</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10559,7 +10559,7 @@
         <v>292</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>292</v>
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
@@ -10592,7 +10592,7 @@
         <v>46223.584198055556</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10643,7 +10643,7 @@
         <v>46223.5841919213</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10671,7 +10671,7 @@
         <v>360</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10694,7 +10694,7 @@
         <v>46223.5841909375</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10722,7 +10722,7 @@
         <v>360</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10745,7 +10745,7 @@
         <v>46223.58419032407</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10773,7 +10773,7 @@
         <v>360</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10796,7 +10796,7 @@
         <v>46223.584189699075</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10824,7 +10824,7 @@
         <v>360</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10847,7 +10847,7 @@
         <v>46223.58418898148</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10875,7 +10875,7 @@
         <v>360</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10898,7 +10898,7 @@
         <v>46223.58418828704</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10926,7 +10926,7 @@
         <v>360</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10949,7 +10949,7 @@
         <v>46223.584187650464</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10977,7 +10977,7 @@
         <v>360</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -11000,7 +11000,7 @@
         <v>46223.58418706019</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11028,7 +11028,7 @@
         <v>360</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -11051,7 +11051,7 @@
         <v>46223.58418637731</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11079,10 +11079,10 @@
         <v>360</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11132,7 +11132,7 @@
         <v>292</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P163" s="10" t="s">
         <v>374</v>
@@ -11150,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11165,7 +11165,7 @@
         <v>46223.584646874995</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11195,7 +11195,7 @@
         <v>373</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>376</v>
@@ -11218,7 +11218,7 @@
         <v>46223.584646261574</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11248,7 +11248,7 @@
         <v>373</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11271,7 +11271,7 @@
         <v>46223.5846455787</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11301,7 +11301,7 @@
         <v>373</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11324,7 +11324,7 @@
         <v>46223.58464490741</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11354,7 +11354,7 @@
         <v>373</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11377,7 +11377,7 @@
         <v>46223.58464418982</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11407,7 +11407,7 @@
         <v>373</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11430,7 +11430,7 @@
         <v>46223.58464350694</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11460,7 +11460,7 @@
         <v>373</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11483,7 +11483,7 @@
         <v>46223.58464282408</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11513,7 +11513,7 @@
         <v>373</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11536,7 +11536,7 @@
         <v>46223.584642118054</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11566,7 +11566,7 @@
         <v>373</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11589,7 +11589,7 @@
         <v>46223.58464141204</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11619,7 +11619,7 @@
         <v>373</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11642,7 +11642,7 @@
         <v>46223.58464068287</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11672,10 +11672,10 @@
         <v>373</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11790,7 +11790,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -11805,7 +11805,7 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11835,7 +11835,7 @@
         <v>390</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>394</v>
@@ -11858,7 +11858,7 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11888,10 +11888,10 @@
         <v>390</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11911,7 +11911,7 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11941,10 +11941,10 @@
         <v>390</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11964,7 +11964,7 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11994,10 +11994,10 @@
         <v>390</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -12017,7 +12017,7 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12047,10 +12047,10 @@
         <v>390</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12070,7 +12070,7 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12100,10 +12100,10 @@
         <v>390</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12123,7 +12123,7 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12153,10 +12153,10 @@
         <v>390</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12176,7 +12176,7 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12206,10 +12206,10 @@
         <v>390</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12229,7 +12229,7 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12259,10 +12259,10 @@
         <v>390</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12282,7 +12282,7 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12312,10 +12312,10 @@
         <v>390</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12365,7 +12365,7 @@
         <v>387</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>387</v>
@@ -12383,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
@@ -12398,7 +12398,7 @@
         <v>46223.58481888889</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12428,7 +12428,7 @@
         <v>405</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>407</v>
@@ -12451,7 +12451,7 @@
         <v>46223.58481829861</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12481,10 +12481,10 @@
         <v>405</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12504,7 +12504,7 @@
         <v>46223.584817662035</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12534,10 +12534,10 @@
         <v>405</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12557,7 +12557,7 @@
         <v>46223.584817083334</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12587,10 +12587,10 @@
         <v>405</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12610,7 +12610,7 @@
         <v>46223.58481644676</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12640,10 +12640,10 @@
         <v>405</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12663,7 +12663,7 @@
         <v>46223.58481584491</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12693,10 +12693,10 @@
         <v>405</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12716,7 +12716,7 @@
         <v>46223.58481525463</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12746,10 +12746,10 @@
         <v>405</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12769,7 +12769,7 @@
         <v>46223.58481465278</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12799,10 +12799,10 @@
         <v>405</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12822,7 +12822,7 @@
         <v>46223.5848140625</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12852,10 +12852,10 @@
         <v>405</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12875,7 +12875,7 @@
         <v>46223.58481342593</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12905,10 +12905,10 @@
         <v>405</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12934,10 +12934,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12956,7 +12956,7 @@
         <v>387</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>387</v>
@@ -12974,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -12989,16 +12989,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13017,7 +13017,7 @@
         <v>418</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>420</v>
@@ -13040,16 +13040,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -13068,10 +13068,10 @@
         <v>418</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13091,16 +13091,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13119,10 +13119,10 @@
         <v>418</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13142,16 +13142,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13170,10 +13170,10 @@
         <v>418</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13193,16 +13193,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13221,10 +13221,10 @@
         <v>418</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13244,16 +13244,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13272,10 +13272,10 @@
         <v>418</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13295,16 +13295,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13323,10 +13323,10 @@
         <v>418</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13346,16 +13346,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13374,10 +13374,10 @@
         <v>418</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13397,16 +13397,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13425,10 +13425,10 @@
         <v>418</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13448,16 +13448,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13476,10 +13476,10 @@
         <v>418</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13505,10 +13505,10 @@
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13529,7 +13529,7 @@
         <v>387</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>432</v>
@@ -13547,7 +13547,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -13562,16 +13562,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13590,7 +13590,7 @@
         <v>431</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>431</v>
@@ -13613,16 +13613,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13641,7 +13641,7 @@
         <v>431</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13664,16 +13664,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13692,7 +13692,7 @@
         <v>431</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13715,16 +13715,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13743,7 +13743,7 @@
         <v>431</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13766,16 +13766,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13794,7 +13794,7 @@
         <v>431</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13817,16 +13817,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13845,7 +13845,7 @@
         <v>431</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13868,16 +13868,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13896,7 +13896,7 @@
         <v>431</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13919,16 +13919,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13947,7 +13947,7 @@
         <v>431</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13970,16 +13970,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13998,7 +13998,7 @@
         <v>431</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -14021,16 +14021,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14049,7 +14049,7 @@
         <v>431</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -14167,7 +14167,7 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -14230,7 +14230,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
